--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:50:20+00:00</t>
+    <t>2026-02-05T15:15:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
 </t>
   </si>
   <si>
-    <t>Commentaire</t>
+    <t>TDDUI Comment</t>
   </si>
   <si>
     <t xml:space="preserve">

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
+++ b/main/ig/StructureDefinition-tddui-related-person-contact.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
